--- a/data/akash_jobs.xlsx
+++ b/data/akash_jobs.xlsx
@@ -536,7 +536,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>2026-09-03 07:31:54</t>
+          <t>2026-09-03 08:49:00</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -607,7 +607,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>2026-09-03 07:31:54</t>
+          <t>2026-09-03 08:49:00</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -678,7 +678,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>2026-09-03 07:31:54</t>
+          <t>2026-09-03 08:49:00</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">

--- a/data/akash_jobs.xlsx
+++ b/data/akash_jobs.xlsx
@@ -536,7 +536,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>2026-09-03 08:49:00</t>
+          <t>2026-09-03 09:26:11</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -607,7 +607,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>2026-09-03 08:49:00</t>
+          <t>2026-09-03 09:26:11</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -678,7 +678,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>2026-09-03 08:49:00</t>
+          <t>2026-09-03 09:26:11</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">

--- a/data/akash_jobs.xlsx
+++ b/data/akash_jobs.xlsx
@@ -536,7 +536,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>2026-09-03 09:26:11</t>
+          <t>2026-09-03 09:50:04</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -607,7 +607,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>2026-09-03 09:26:11</t>
+          <t>2026-09-03 09:50:04</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -678,7 +678,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>2026-09-03 09:26:11</t>
+          <t>2026-09-03 09:50:04</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">

--- a/data/akash_jobs.xlsx
+++ b/data/akash_jobs.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O4"/>
+  <dimension ref="A1:O29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -496,32 +496,32 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>78a6d7560ddbd4caa774</t>
+          <t>2f178d32b572fd3a4fb7</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Acme Services Private Limited</t>
+          <t>Amazon India</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>AI Engineer</t>
+          <t>Software development Engineer</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Richmond Town, Bangalore</t>
+          <t>Bangalore, Karnataka</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Job Description: Build application-facing AI features powered by LLMs, agentic workflows, and AI orchestration platforms. Integrate with MLOps-managed agents and consume LLM capabilities through AI Gateway patterns including routing, authentication, policy controls, and logging. Design and implement</t>
+          <t>Role - Software Development Engineer-2 As a Software Development Engineer at Amazon, you have industry-leading technical abilities and demonstrate breadth and depth of knowledge. You build software to deliver business impact, making smart technology choices. You work in a team and drive things forwa</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>https://www.adzuna.in/details/5863107008?utm_medium=api&amp;utm_source=447522e9</t>
+          <t>https://www.adzuna.in/details/2698332543?utm_medium=api&amp;utm_source=447522e9</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -531,17 +531,17 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2026-09-03 07:31:54</t>
+          <t>2026-09-03 12:39:34</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>2026-09-03 09:50:04</t>
+          <t>2026-09-03 12:39:34</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>3337532b20885bd1775f</t>
+          <t>d20d089e4082b894148f</t>
         </is>
       </c>
       <c r="K2" t="n">
@@ -549,7 +549,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>skill:LLM, skill:MCP</t>
+          <t>skill:C++, skill:Java</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -567,32 +567,32 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>f65350a6483821dfdd3a</t>
+          <t>8ea05990f9754e320d09</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Acme Services Private Limited</t>
+          <t>Multi Recruit</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>AI Engineer</t>
+          <t>Software Development Engineer</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Richmond Town, Bangalore</t>
+          <t>Bangalore, Karnataka</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Job Description: Build and deploy production-grade AI and Agentic AI solutions for client business use cases. Design and implement AI agent workflows using LangGraph, CrewAI, and cloud-based agent platforms. Develop and manage AI/ML pipelines, including RAG, multi-agent orchestration, evaluation, an</t>
+          <t>Computer Science fundamentals in object-oriented design, design patterns, data structures, algorithm design, Proficiency with Java 1 years of experience contributing to architecture and design in a product setup Key Responsibilities Understand customer needs by collaborating with Product Managers an</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>https://www.adzuna.in/details/5865169480?utm_medium=api&amp;utm_source=447522e9</t>
+          <t>https://www.adzuna.in/details/2171039159?utm_medium=api&amp;utm_source=447522e9</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -602,25 +602,25 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2026-09-03 07:31:54</t>
+          <t>2026-09-03 12:39:34</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>2026-09-03 09:50:04</t>
+          <t>2026-09-03 12:39:34</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>1463f44c91d7b4c9c45f</t>
+          <t>e4ec4857e5f35fa49afb</t>
         </is>
       </c>
       <c r="K3" t="n">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>skill:RAG, skill:MCP, skill:AI Agents, skill:Agentic AI</t>
+          <t>skill:Java, skill:Data Structures</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -638,17 +638,17 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>758e789b17e2f7dd6c51</t>
+          <t>4192f4ba5cd34f31bfd6</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Jothishi Online and Advertising Services Private Limited</t>
+          <t>Publicis Sapient</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>AI Engineer</t>
+          <t>Software Development Engineer</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -658,12 +658,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AI ENGINEER – RETROGRADE AI Generative AI | LLMs | RAG | AI Agents | Vedic Astrology Company: JOTHISHI Online &amp; Advertising Services Pvt. Ltd. Product: RetroGrade AI Website: https://retrograde.co.in/ Location: Bengaluru / Hybrid / Remote Employment: Full-Time About RetroGrade AI RetroGrade AI , fro</t>
+          <t xml:space="preserve">Experience building large scale, large volume services &amp; distributed apps., taking them through production and post-production life cycles Experience in Programming Language: Java 8, Javascript Experience in Microservice Development or Architecture Experience with Web Application Frameworks: Spring </t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>https://www.adzuna.in/details/5842544539?utm_medium=api&amp;utm_source=447522e9</t>
+          <t>https://www.adzuna.in/details/3183166626?utm_medium=api&amp;utm_source=447522e9</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -673,17 +673,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2026-09-03 07:31:54</t>
+          <t>2026-09-03 12:39:34</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>2026-09-03 09:50:04</t>
+          <t>2026-09-03 12:39:34</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>088a26264467b471f752</t>
+          <t>e69c2cce94a9243da0e9</t>
         </is>
       </c>
       <c r="K4" t="n">
@@ -691,20 +691,1795 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
+          <t>skill:Java, skill:JavaScript</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>565e04fd2b406ecb5ad5</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Multi Recruit</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Software Development Engineer</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Bangalore, Karnataka</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Bachelor's degree in Computer Science (BE/ B.Tech) Strong computer science fundamentals in algorithms, data structures, storage technologies, distributed computing, operating systems, etc. Experience in designing and implementing scalable solutions in a large scale distributed environment. Robust an</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>https://www.adzuna.in/details/2853928132?utm_medium=api&amp;utm_source=447522e9</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>adzuna</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>2026-09-03 12:39:34</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>2026-09-03 12:39:34</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>a93dbd277d84ed26d792</t>
+        </is>
+      </c>
+      <c r="K5" t="n">
+        <v>30</v>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>skill:Java, skill:Data Structures, skill:Algorithms</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>b625a406d8d76e189728</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Success Pact</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>SDE</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Bangalore, Karnataka</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Hi, Good exp in data structures, Java, algorithms, and in design, design patterns. Exp-2-8yrs Location- Bangalore, hyderabad, pune, gurgaon. Regards sanchita Skills:- Data Structures, Algorithms, Design patterns and Java</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>https://www.adzuna.in/details/1517699787?utm_medium=api&amp;utm_source=447522e9</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>adzuna</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>2026-09-03 12:39:34</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>2026-09-03 12:39:34</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>4cba866bcbd6995043c8</t>
+        </is>
+      </c>
+      <c r="K6" t="n">
+        <v>30</v>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>skill:Java, skill:Data Structures, skill:Algorithms</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>ebc5b006922ab6a2c56e</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Infosys Limited</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Full Stack Associate developer</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Bangalore, Karnataka</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Key Responsibilities: Design develop and deploy AI enabled web applications using modern front end backend database and cloud technologies Build responsive reusable and user friendly interfaces using component based JavaScript frameworks such as React Develop scalable backend services REST APIs and </t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>https://www.adzuna.in/details/5856196415?utm_medium=api&amp;utm_source=447522e9</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>adzuna</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>2026-09-03 12:39:34</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>2026-09-03 12:39:34</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>f8e73b9c27788eb353dc</t>
+        </is>
+      </c>
+      <c r="K7" t="n">
+        <v>30</v>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>skill:Python, skill:JavaScript, skill:REST APIs</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>899a1946f5ce36ff7540</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Infosys Limited</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>SAP ABAP Developer</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Bangalore, Karnataka</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Key Responsibilities: A day in the life of an Infoscion As part of the Infosys delivery team your primary role would be to ensure effective Design Development Validation and Support activities to assure that our clients are satisfied with the high levels of service in the technology domain You will </t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>https://www.adzuna.in/details/5856196906?utm_medium=api&amp;utm_source=447522e9</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>adzuna</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>2026-09-03 12:39:34</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>2026-09-03 12:39:34</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>e26666f41716fa855c3f</t>
+        </is>
+      </c>
+      <c r="K8" t="n">
+        <v>20</v>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>skill:ABAP, skill:SAP ABAP</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>5746ba43221b515015c3</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>BDI India private limited</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>SAP ABAP Developer</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Bangalore, Karnataka</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Should have Worked extensively on SAP developments including the Application Design and Document for Custom development , in end to end SAP Implementation. Preparation of Technical Spec and Unit Test documents . Hands on experience and extensive knowledge on RICEF (Reports , ALE/IDOC, BDC ,Userexit </t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>https://www.adzuna.in/details/3693772439?utm_medium=api&amp;utm_source=447522e9</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>adzuna</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>2026-09-03 12:39:34</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>2026-09-03 12:39:34</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>4a42739ed4e517074713</t>
+        </is>
+      </c>
+      <c r="K9" t="n">
+        <v>20</v>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>skill:ABAP, skill:SAP ABAP</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>850148a4bcb069a870cf</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>RAPIDD Technologies</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>SAP ABAP Developer</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Bangalore, Karnataka</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Coolest SAP-ABAP roles in town We work with the "heppest" and most happening companies in the world we deal with the daily and long-term concerns of celebrities, sportspeople, managers, financiers, insurers and entrepreneurs. We have provided long-playing solutions for them on the Web, the enterpris</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>https://www.adzuna.in/details/1155088979?utm_medium=api&amp;utm_source=447522e9</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>adzuna</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>2026-09-03 12:39:34</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>2026-09-03 12:39:34</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>4481b5a0e20e9814d9fc</t>
+        </is>
+      </c>
+      <c r="K10" t="n">
+        <v>20</v>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>skill:ABAP, skill:SAP ABAP</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>b858d64fbd97c54baa17</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Infosys Limited</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>SAP ABAP Developer</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Bangalore, Karnataka</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Key Responsibilities: A day in the life of an Infoscion As part of the Infosys delivery team your primary role would be to interface with the client for quality assurance issue resolution and ensuring high customer satisfaction You will understand requirements create and review designs validate the </t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>https://www.adzuna.in/details/5856196926?utm_medium=api&amp;utm_source=447522e9</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>adzuna</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>2026-09-03 12:39:34</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>2026-09-03 12:39:34</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>b4934b8ade7563c5b7f3</t>
+        </is>
+      </c>
+      <c r="K11" t="n">
+        <v>20</v>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>skill:ABAP, skill:SAP ABAP</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>78a6d7560ddbd4caa774</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Acme Services Private Limited</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>AI Engineer</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Richmond Town, Bangalore</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Job Description: Build application-facing AI features powered by LLMs, agentic workflows, and AI orchestration platforms. Integrate with MLOps-managed agents and consume LLM capabilities through AI Gateway patterns including routing, authentication, policy controls, and logging. Design and implement</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>https://www.adzuna.in/details/5863107008?utm_medium=api&amp;utm_source=447522e9</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>adzuna</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>2026-09-03 07:31:54</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>2026-09-03 12:39:34</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>3337532b20885bd1775f</t>
+        </is>
+      </c>
+      <c r="K12" t="n">
+        <v>20</v>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>skill:LLM, skill:MCP</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>f65350a6483821dfdd3a</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Acme Services Private Limited</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>AI Engineer</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Richmond Town, Bangalore</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Job Description: Build and deploy production-grade AI and Agentic AI solutions for client business use cases. Design and implement AI agent workflows using LangGraph, CrewAI, and cloud-based agent platforms. Develop and manage AI/ML pipelines, including RAG, multi-agent orchestration, evaluation, an</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>https://www.adzuna.in/details/5865169480?utm_medium=api&amp;utm_source=447522e9</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>adzuna</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>2026-09-03 07:31:54</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>2026-09-03 12:39:34</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>1463f44c91d7b4c9c45f</t>
+        </is>
+      </c>
+      <c r="K13" t="n">
+        <v>40</v>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>skill:RAG, skill:MCP, skill:AI Agents, skill:Agentic AI</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>758e789b17e2f7dd6c51</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Jothishi Online and Advertising Services Private Limited</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>AI Engineer</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Bangalore, Karnataka</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>AI ENGINEER – RETROGRADE AI Generative AI | LLMs | RAG | AI Agents | Vedic Astrology Company: JOTHISHI Online &amp; Advertising Services Pvt. Ltd. Product: RetroGrade AI Website: https://retrograde.co.in/ Location: Bengaluru / Hybrid / Remote Employment: Full-Time About RetroGrade AI RetroGrade AI , fro</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>https://www.adzuna.in/details/5842544539?utm_medium=api&amp;utm_source=447522e9</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>adzuna</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>2026-09-03 07:31:54</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>2026-09-03 12:39:34</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>088a26264467b471f752</t>
+        </is>
+      </c>
+      <c r="K14" t="n">
+        <v>20</v>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
           <t>skill:RAG, skill:AI Agents</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>6a86976e47b299fab013</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Qure Ai</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>LLM Engineer</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Bangalore, Karnataka</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Key Responsibilities: Design and implement LLM-based features across Qure's products, including clinician-facing assistants and automated diagnostic flows. Build internal tools, APIs, and developer-facing utilities to enable scalable LLM integrations. Collaborate with prompt engineers to design modu</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>https://www.adzuna.in/details/5850380109?utm_medium=api&amp;utm_source=447522e9</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>adzuna</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>2026-09-03 12:39:34</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>2026-09-03 12:39:34</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>870b4467a51bf482716e</t>
+        </is>
+      </c>
+      <c r="K15" t="n">
+        <v>20</v>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>skill:LLM, skill:RAG</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>7485318972c6a8fdc903</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Evalueserve.com Private Limited</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>NLP &amp; LLM Engineer</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Bangalore, Karnataka</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Description We are seeking an experienced NLP &amp; LLM Engineer to join our team in India. The ideal candidate will be responsible for designing and implementing advanced NLP models and algorithms, as well as developing and fine-tuning large language models for various applications. This role requires </t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>https://www.adzuna.in/details/5859117816?utm_medium=api&amp;utm_source=447522e9</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>adzuna</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>2026-09-03 12:39:34</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>2026-09-03 12:39:34</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>1f7f4b514835031b53fb</t>
+        </is>
+      </c>
+      <c r="K16" t="n">
+        <v>30</v>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>skill:LLM, skill:Fine-tuning, skill:Algorithms</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>f946199f8d0d3b0b48b4</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Infosys Limited</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Gen AI Engineer</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Bangalore, Karnataka</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Job Description: We are seeking a highly motivated Generative AI LLMOps Engineer with hands on experience in building deploying monitoring and optimizing Large Language Model LLM applications in production environments The ideal candidate should have strong expertise in Generative AI LLMOps RAG fram</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>https://www.adzuna.in/details/5856196537?utm_medium=api&amp;utm_source=447522e9</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>adzuna</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>2026-09-03 12:39:34</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>2026-09-03 12:39:34</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>14f71f1f1b25897aaaa3</t>
+        </is>
+      </c>
+      <c r="K17" t="n">
+        <v>20</v>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>skill:LLM, skill:RAG</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>016e1189f8ee343d58ce</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Infosys Limited</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Junior AI Engineer</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Bangalore, Karnataka</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Job Description: We are looking for a Python AI Engineer 2 3 yrs who can build and productionize AI GenAI solutions especially LLM powered applications such as RAG systems summarization classification and agentic workflows The role is engineering led strong Python coding API development deployment r</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>https://www.adzuna.in/details/5773093473?utm_medium=api&amp;utm_source=447522e9</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>adzuna</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>2026-09-03 12:39:34</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>2026-09-03 12:39:34</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>5ae5f3d7c0df631f6457</t>
+        </is>
+      </c>
+      <c r="K18" t="n">
+        <v>30</v>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>skill:Python, skill:LLM, skill:RAG</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>bedebd0e647137fbab9e</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Zorba Consulting India</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Python Developer</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Bangalore, Karnataka</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Role Overview We are looking for an experienced Python Developer with strong hands-on expertise in Python coding, Streamlit, Flask, and FastAPI . The candidate will be responsible for developing Python-based services, Streamlit applications, automation scripts, API integrations, and data-processing </t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>https://www.adzuna.in/details/5857693060?utm_medium=api&amp;utm_source=447522e9</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>adzuna</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>2026-09-03 12:39:34</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>2026-09-03 12:39:34</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>443a693318c3c6f3b107</t>
+        </is>
+      </c>
+      <c r="K19" t="n">
+        <v>20</v>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>skill:Python, skill:SQL</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>78723e7ad5a8abc08a88</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Conneqt Business Solutions Limited</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Python Developer</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Bangalore, Karnataka</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Required Skills and Qualifications: • Strong experience in Python for backend development. • Proficiency in MSSQL and writing optimized SQL queries and stored procedures. • Hands-on experience with Redis and Celery for task queues and caching. • Expertise in RabbitMQ for messaging systems. • Practic</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>https://www.adzuna.in/details/5806699867?utm_medium=api&amp;utm_source=447522e9</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>adzuna</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>2026-09-03 12:39:34</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>2026-09-03 12:39:34</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>72e4255119e60b04397d</t>
+        </is>
+      </c>
+      <c r="K20" t="n">
+        <v>30</v>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>skill:Python, skill:SQL, skill:Git</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>e064c2f26e0ad99ea307</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Freelancer</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>AI Platform Engineer</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Bangalore, Karnataka</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Primary Skills Observability: ELK (Elasticsearch/Kibana), Prometheus, Grafana, PromQL Automation: Java/Vert.x or Python (FastAPI), Shell/Bash, REST/SOAP APIs Cloud &amp; Platform: Docker, Kubernetes, Kafka, Redis Reliability Engineering: Distributed Systems, Microservices, Event-Driven Architecture, DR </t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>https://www.adzuna.in/details/5819667613?utm_medium=api&amp;utm_source=447522e9</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>adzuna</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>2026-09-03 12:39:34</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>2026-09-03 12:39:34</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>8598b9c94bbd4b69cef7</t>
+        </is>
+      </c>
+      <c r="K21" t="n">
+        <v>70</v>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>skill:Python, skill:Java, skill:LLM, skill:RAG, skill:MCP, skill:LangChain, skill:Agentic AI</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>af50c92173adc37c2987</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Ampera Technologies</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Cloud &amp; AI Platform Engineer</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Bangalore, Karnataka</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Job Description: We are seeking a Cloud &amp; AI Platform Engineer to design and operate AI-native infrastructure that supports large-scale machine learning, generative AI, and agentic AI systems. This role will focus on building secure, scalable, and automated multi-cloud platforms across AWS, Azure, G</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>https://www.adzuna.in/details/5743193223?utm_medium=api&amp;utm_source=447522e9</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>adzuna</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>2026-09-03 12:39:34</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>2026-09-03 12:39:34</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>e93b807a80dea78003e5</t>
+        </is>
+      </c>
+      <c r="K22" t="n">
+        <v>30</v>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>skill:LLM, skill:AI Agents, skill:Agentic AI</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>311fb19fb00f4911e61d</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Infosys Limited</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Agentic AI Engineer</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Bangalore, Karnataka</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Job Description: We are looking for an Agentic AI Engineer to design and build intelligent autonomous AI agents capable of reasoning planning and executing tasks in dynamic environments This role involves working with cutting edge LLMs multi agent frameworks and integrating them into enterprise work</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>https://www.adzuna.in/details/5856196683?utm_medium=api&amp;utm_source=447522e9</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>adzuna</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>2026-09-03 12:39:34</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>2026-09-03 12:39:34</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>b4d86688855294caa1f5</t>
+        </is>
+      </c>
+      <c r="K23" t="n">
+        <v>20</v>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>skill:AI Agents, skill:Agentic AI</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>cf0c42e653989652a580</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Infosys Limited</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Agentic AI Engineer</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Bangalore, Karnataka</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Job Description: We are seeking a talented and enthusiastic Generative AI Engineer to join our growing AI practice The ideal candidate should have hands on experience in developing Generative AI solutions using Large Language Models LLMs Retrieval Augmented Generation RAG and Python Exposure to clou</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>https://www.adzuna.in/details/5856196541?utm_medium=api&amp;utm_source=447522e9</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>adzuna</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>2026-09-03 12:39:34</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>2026-09-03 12:39:34</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>27a48387e067aa38e2bf</t>
+        </is>
+      </c>
+      <c r="K24" t="n">
+        <v>30</v>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>skill:Python, skill:RAG, skill:Agentic AI</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>9ee7c8bccd18fb65df78</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Deqode</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>GenAI &amp; Agentic AI Engineer</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Bangalore, Karnataka</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Role Summary We are seeking a skilled GenAI &amp; Agentic AI Engineer with strong experience in building end‑to‑end AI/ML solutions, Generative AI applications, and agent‑based automation workflows. The ideal candidate will have a solid background in machine learning along with hands‑on expertise in LLM</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>https://www.adzuna.in/details/5818254504?utm_medium=api&amp;utm_source=447522e9</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>adzuna</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>2026-09-03 12:39:34</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>2026-09-03 12:39:34</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>03332746a9e8bdbcf53b</t>
+        </is>
+      </c>
+      <c r="K25" t="n">
+        <v>40</v>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>skill:RAG, skill:Vector Databases, skill:LangChain, skill:Agentic AI</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>fa3e1a42cbbcfe984440</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Techwise Digital</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Generative AI &amp; Agentic AI Engineer</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Bangalore, Karnataka</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>We are seeking a skilled Generative AI Engineer to develop and deploy intelligent, production-ready AI applications using LLMs and agent-based architectures. The candidate will work on building solutions that combine enterprise data, APIs, knowledge repositories, and AI models to solve real-world bu</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>https://www.adzuna.in/details/5860488267?utm_medium=api&amp;utm_source=447522e9</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>adzuna</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>2026-09-03 12:39:34</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>2026-09-03 12:39:34</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>ea1aa592417dcf430ddd</t>
+        </is>
+      </c>
+      <c r="K26" t="n">
+        <v>30</v>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>skill:Python, skill:RAG, skill:Agentic AI</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>cf2732cd1a39a42758bf</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Levi Strauss</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>SAP Retail &amp; Supply Chain - Agentic AI Engineer</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Bangalore, Karnataka</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Job Location: Warsaw, Poland Calling all originals: At Levi Strauss &amp; Co., you can be yourself — and be part of something bigger. We’re a company of people who like to forge our own path and leave the world better than we found it. Who believe that what makes us different makes us stronger. So add y</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>https://www.adzuna.in/details/5856965767?utm_medium=api&amp;utm_source=447522e9</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>adzuna</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>2026-09-03 12:39:34</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>2026-09-03 12:39:34</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>449076581da53b8b0e2c</t>
+        </is>
+      </c>
+      <c r="K27" t="n">
+        <v>20</v>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>skill:AI Agents, skill:Agentic AI</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>be9947e662597926015b</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Trigent Software Private Limited</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Full Stack Engineer</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Richmond Town, Bangalore</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Must-Have Skills Frontend Strong JavaScript fundamentals (ES6, async/await, closures) React experience preferred (hooks, state management, component architecture) Backend Proficient in Python, writing production-grade code Hands-on experience with FastAPI or Flask for building REST APIs Database Exp</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>https://www.adzuna.in/details/5867507549?utm_medium=api&amp;utm_source=447522e9</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>adzuna</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>2026-09-03 12:39:34</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>2026-09-03 12:39:34</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>f5812926dbe4c720e676</t>
+        </is>
+      </c>
+      <c r="K28" t="n">
+        <v>40</v>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>skill:Python, skill:JavaScript, skill:SQL, skill:REST APIs</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>4cabe1a20fc46c23e821</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Trigent Software Private Limited</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Full Stack Engineer</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Richmond Town, Bangalore</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Must-Have Skills Frontend Strong JavaScript fundamentals (ES6, async/await, closures) React experience preferred (hooks, state management, component architecture) Backend Proficient in Python, writing production-grade code Hands-on experience with FastAPI or Flask for building REST APIs Database Exp</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>https://www.adzuna.in/details/5867507551?utm_medium=api&amp;utm_source=447522e9</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>adzuna</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>2026-09-03 12:39:34</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>2026-09-03 12:39:34</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>f5812926dbe4c720e676</t>
+        </is>
+      </c>
+      <c r="K29" t="n">
+        <v>40</v>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>skill:Python, skill:JavaScript, skill:SQL, skill:REST APIs</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O29" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/akash_jobs.xlsx
+++ b/data/akash_jobs.xlsx
@@ -536,7 +536,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>2026-09-03 12:39:34</t>
+          <t>2026-09-03 13:19:59</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -607,7 +607,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>2026-09-03 12:39:34</t>
+          <t>2026-09-03 13:19:59</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -678,7 +678,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>2026-09-03 12:39:34</t>
+          <t>2026-09-03 13:19:59</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -749,7 +749,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>2026-09-03 12:39:34</t>
+          <t>2026-09-03 13:19:59</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -820,7 +820,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>2026-09-03 12:39:34</t>
+          <t>2026-09-03 13:19:59</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -891,7 +891,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>2026-09-03 12:39:34</t>
+          <t>2026-09-03 13:19:59</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -962,7 +962,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>2026-09-03 12:39:34</t>
+          <t>2026-09-03 13:19:59</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1033,7 +1033,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>2026-09-03 12:39:34</t>
+          <t>2026-09-03 13:19:59</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>2026-09-03 12:39:34</t>
+          <t>2026-09-03 13:19:59</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1175,7 +1175,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>2026-09-03 12:39:34</t>
+          <t>2026-09-03 13:19:59</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1246,7 +1246,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>2026-09-03 12:39:34</t>
+          <t>2026-09-03 13:19:59</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1317,7 +1317,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>2026-09-03 12:39:34</t>
+          <t>2026-09-03 13:19:59</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -1388,7 +1388,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>2026-09-03 12:39:34</t>
+          <t>2026-09-03 13:19:59</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -1459,7 +1459,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>2026-09-03 12:39:34</t>
+          <t>2026-09-03 13:19:59</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -1530,7 +1530,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>2026-09-03 12:39:34</t>
+          <t>2026-09-03 13:19:59</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -1601,7 +1601,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>2026-09-03 12:39:34</t>
+          <t>2026-09-03 13:19:59</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -1672,7 +1672,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>2026-09-03 12:39:34</t>
+          <t>2026-09-03 13:19:59</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -1743,7 +1743,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>2026-09-03 12:39:34</t>
+          <t>2026-09-03 13:19:59</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -1814,7 +1814,7 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>2026-09-03 12:39:34</t>
+          <t>2026-09-03 13:19:59</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -1885,7 +1885,7 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>2026-09-03 12:39:34</t>
+          <t>2026-09-03 13:19:59</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>2026-09-03 12:39:34</t>
+          <t>2026-09-03 13:19:59</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -2027,7 +2027,7 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>2026-09-03 12:39:34</t>
+          <t>2026-09-03 13:19:59</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -2098,7 +2098,7 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>2026-09-03 12:39:34</t>
+          <t>2026-09-03 13:19:59</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -2169,7 +2169,7 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>2026-09-03 12:39:34</t>
+          <t>2026-09-03 13:19:59</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -2240,7 +2240,7 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>2026-09-03 12:39:34</t>
+          <t>2026-09-03 13:19:59</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -2311,7 +2311,7 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>2026-09-03 12:39:34</t>
+          <t>2026-09-03 13:19:59</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>2026-09-03 12:39:34</t>
+          <t>2026-09-03 13:19:59</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -2453,7 +2453,7 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>2026-09-03 12:39:34</t>
+          <t>2026-09-03 13:19:59</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">

--- a/data/akash_jobs.xlsx
+++ b/data/akash_jobs.xlsx
@@ -536,7 +536,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>2026-09-03 13:19:59</t>
+          <t>2026-09-03 14:42:20</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -607,7 +607,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>2026-09-03 13:19:59</t>
+          <t>2026-09-03 14:42:20</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -678,7 +678,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>2026-09-03 13:19:59</t>
+          <t>2026-09-03 14:42:20</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -749,7 +749,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>2026-09-03 13:19:59</t>
+          <t>2026-09-03 14:42:20</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -820,7 +820,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>2026-09-03 13:19:59</t>
+          <t>2026-09-03 14:42:20</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -891,7 +891,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>2026-09-03 13:19:59</t>
+          <t>2026-09-03 14:42:20</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -962,7 +962,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>2026-09-03 13:19:59</t>
+          <t>2026-09-03 14:42:20</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1033,7 +1033,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>2026-09-03 13:19:59</t>
+          <t>2026-09-03 14:42:20</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>2026-09-03 13:19:59</t>
+          <t>2026-09-03 14:42:20</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1175,7 +1175,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>2026-09-03 13:19:59</t>
+          <t>2026-09-03 14:42:20</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1246,7 +1246,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>2026-09-03 13:19:59</t>
+          <t>2026-09-03 14:42:20</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1317,7 +1317,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>2026-09-03 13:19:59</t>
+          <t>2026-09-03 14:42:20</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -1388,7 +1388,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>2026-09-03 13:19:59</t>
+          <t>2026-09-03 14:42:20</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -1459,7 +1459,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>2026-09-03 13:19:59</t>
+          <t>2026-09-03 14:42:20</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -1530,7 +1530,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>2026-09-03 13:19:59</t>
+          <t>2026-09-03 14:42:20</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -1601,7 +1601,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>2026-09-03 13:19:59</t>
+          <t>2026-09-03 14:42:20</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -1672,7 +1672,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>2026-09-03 13:19:59</t>
+          <t>2026-09-03 14:42:20</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -1743,7 +1743,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>2026-09-03 13:19:59</t>
+          <t>2026-09-03 14:42:20</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -1814,7 +1814,7 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>2026-09-03 13:19:59</t>
+          <t>2026-09-03 14:42:20</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -1885,7 +1885,7 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>2026-09-03 13:19:59</t>
+          <t>2026-09-03 14:42:20</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>2026-09-03 13:19:59</t>
+          <t>2026-09-03 14:42:20</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -2027,7 +2027,7 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>2026-09-03 13:19:59</t>
+          <t>2026-09-03 14:42:20</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -2098,7 +2098,7 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>2026-09-03 13:19:59</t>
+          <t>2026-09-03 14:42:20</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -2169,7 +2169,7 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>2026-09-03 13:19:59</t>
+          <t>2026-09-03 14:42:20</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -2240,7 +2240,7 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>2026-09-03 13:19:59</t>
+          <t>2026-09-03 14:42:20</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -2311,7 +2311,7 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>2026-09-03 13:19:59</t>
+          <t>2026-09-03 14:42:20</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>2026-09-03 13:19:59</t>
+          <t>2026-09-03 14:42:20</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -2453,7 +2453,7 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>2026-09-03 13:19:59</t>
+          <t>2026-09-03 14:42:20</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">

--- a/data/akash_jobs.xlsx
+++ b/data/akash_jobs.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O29"/>
+  <dimension ref="A1:O30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -536,7 +536,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>2026-09-03 14:42:20</t>
+          <t>2026-09-03 16:28:32</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -607,7 +607,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>2026-09-03 14:42:20</t>
+          <t>2026-09-03 16:28:32</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -678,7 +678,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>2026-09-03 14:42:20</t>
+          <t>2026-09-03 16:28:32</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -749,7 +749,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>2026-09-03 14:42:20</t>
+          <t>2026-09-03 16:28:32</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -820,7 +820,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>2026-09-03 14:42:20</t>
+          <t>2026-09-03 16:28:32</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -891,7 +891,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>2026-09-03 14:42:20</t>
+          <t>2026-09-03 16:28:32</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -962,7 +962,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>2026-09-03 14:42:20</t>
+          <t>2026-09-03 16:28:32</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1033,7 +1033,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>2026-09-03 14:42:20</t>
+          <t>2026-09-03 16:28:32</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>2026-09-03 14:42:20</t>
+          <t>2026-09-03 16:28:32</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1175,7 +1175,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>2026-09-03 14:42:20</t>
+          <t>2026-09-03 16:28:32</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1246,7 +1246,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>2026-09-03 14:42:20</t>
+          <t>2026-09-03 16:28:32</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1317,7 +1317,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>2026-09-03 14:42:20</t>
+          <t>2026-09-03 16:28:32</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -1388,7 +1388,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>2026-09-03 14:42:20</t>
+          <t>2026-09-03 16:28:32</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -1459,7 +1459,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>2026-09-03 14:42:20</t>
+          <t>2026-09-03 16:28:32</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -1530,7 +1530,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>2026-09-03 14:42:20</t>
+          <t>2026-09-03 16:28:32</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -1561,17 +1561,17 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>f946199f8d0d3b0b48b4</t>
+          <t>7af5893a4a557dcae243</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Infosys Limited</t>
+          <t>Ecolibrium</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Gen AI Engineer</t>
+          <t>AI Engineer – ML, LLM &amp; Agentic AI</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -1581,12 +1581,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Job Description: We are seeking a highly motivated Generative AI LLMOps Engineer with hands on experience in building deploying monitoring and optimizing Large Language Model LLM applications in production environments The ideal candidate should have strong expertise in Generative AI LLMOps RAG fram</t>
+          <t>We are looking for an AI Engineer who can build intelligent systems end-to-end, working across Machine Learning, LLMs, Generative AI, Agentic AI, model development, fine-tuning and production AI systems. This is a hands-on engineering role: you will take ambiguous problems, determine the right AI ap</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>https://www.adzuna.in/details/5856196537?utm_medium=api&amp;utm_source=447522e9</t>
+          <t>https://www.adzuna.in/details/5869199772?utm_medium=api&amp;utm_source=447522e9</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -1596,25 +1596,25 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>2026-09-03 12:39:34</t>
+          <t>2026-09-03 16:28:32</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>2026-09-03 14:42:20</t>
+          <t>2026-09-03 16:28:32</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>14f71f1f1b25897aaaa3</t>
+          <t>7a5aa7cdbaaf38a30001</t>
         </is>
       </c>
       <c r="K17" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>skill:LLM, skill:RAG</t>
+          <t>skill:LLM, skill:Fine-tuning, skill:Agentic AI</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
@@ -1632,7 +1632,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>016e1189f8ee343d58ce</t>
+          <t>f946199f8d0d3b0b48b4</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1642,7 +1642,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Junior AI Engineer</t>
+          <t>Gen AI Engineer</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -1652,12 +1652,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Job Description: We are looking for a Python AI Engineer 2 3 yrs who can build and productionize AI GenAI solutions especially LLM powered applications such as RAG systems summarization classification and agentic workflows The role is engineering led strong Python coding API development deployment r</t>
+          <t>Job Description: We are seeking a highly motivated Generative AI LLMOps Engineer with hands on experience in building deploying monitoring and optimizing Large Language Model LLM applications in production environments The ideal candidate should have strong expertise in Generative AI LLMOps RAG fram</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>https://www.adzuna.in/details/5773093473?utm_medium=api&amp;utm_source=447522e9</t>
+          <t>https://www.adzuna.in/details/5856196537?utm_medium=api&amp;utm_source=447522e9</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -1672,20 +1672,20 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>2026-09-03 14:42:20</t>
+          <t>2026-09-03 16:28:32</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>5ae5f3d7c0df631f6457</t>
+          <t>14f71f1f1b25897aaaa3</t>
         </is>
       </c>
       <c r="K18" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>skill:Python, skill:LLM, skill:RAG</t>
+          <t>skill:LLM, skill:RAG</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
@@ -1703,17 +1703,17 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>bedebd0e647137fbab9e</t>
+          <t>016e1189f8ee343d58ce</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Zorba Consulting India</t>
+          <t>Infosys Limited</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Python Developer</t>
+          <t>Junior AI Engineer</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -1723,12 +1723,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t xml:space="preserve">Role Overview We are looking for an experienced Python Developer with strong hands-on expertise in Python coding, Streamlit, Flask, and FastAPI . The candidate will be responsible for developing Python-based services, Streamlit applications, automation scripts, API integrations, and data-processing </t>
+          <t>Job Description: We are looking for a Python AI Engineer 2 3 yrs who can build and productionize AI GenAI solutions especially LLM powered applications such as RAG systems summarization classification and agentic workflows The role is engineering led strong Python coding API development deployment r</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>https://www.adzuna.in/details/5857693060?utm_medium=api&amp;utm_source=447522e9</t>
+          <t>https://www.adzuna.in/details/5773093473?utm_medium=api&amp;utm_source=447522e9</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -1743,20 +1743,20 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>2026-09-03 14:42:20</t>
+          <t>2026-09-03 16:28:32</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>443a693318c3c6f3b107</t>
+          <t>5ae5f3d7c0df631f6457</t>
         </is>
       </c>
       <c r="K19" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>skill:Python, skill:SQL</t>
+          <t>skill:Python, skill:LLM, skill:RAG</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
@@ -1774,12 +1774,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>78723e7ad5a8abc08a88</t>
+          <t>bedebd0e647137fbab9e</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Conneqt Business Solutions Limited</t>
+          <t>Zorba Consulting India</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1794,12 +1794,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Required Skills and Qualifications: • Strong experience in Python for backend development. • Proficiency in MSSQL and writing optimized SQL queries and stored procedures. • Hands-on experience with Redis and Celery for task queues and caching. • Expertise in RabbitMQ for messaging systems. • Practic</t>
+          <t xml:space="preserve">Role Overview We are looking for an experienced Python Developer with strong hands-on expertise in Python coding, Streamlit, Flask, and FastAPI . The candidate will be responsible for developing Python-based services, Streamlit applications, automation scripts, API integrations, and data-processing </t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>https://www.adzuna.in/details/5806699867?utm_medium=api&amp;utm_source=447522e9</t>
+          <t>https://www.adzuna.in/details/5857693060?utm_medium=api&amp;utm_source=447522e9</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -1814,20 +1814,20 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>2026-09-03 14:42:20</t>
+          <t>2026-09-03 16:28:32</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>72e4255119e60b04397d</t>
+          <t>443a693318c3c6f3b107</t>
         </is>
       </c>
       <c r="K20" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>skill:Python, skill:SQL, skill:Git</t>
+          <t>skill:Python, skill:SQL</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
@@ -1845,17 +1845,17 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>e064c2f26e0ad99ea307</t>
+          <t>78723e7ad5a8abc08a88</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Freelancer</t>
+          <t>Conneqt Business Solutions Limited</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>AI Platform Engineer</t>
+          <t>Python Developer</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -1865,12 +1865,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t xml:space="preserve">Primary Skills Observability: ELK (Elasticsearch/Kibana), Prometheus, Grafana, PromQL Automation: Java/Vert.x or Python (FastAPI), Shell/Bash, REST/SOAP APIs Cloud &amp; Platform: Docker, Kubernetes, Kafka, Redis Reliability Engineering: Distributed Systems, Microservices, Event-Driven Architecture, DR </t>
+          <t>Required Skills and Qualifications: • Strong experience in Python for backend development. • Proficiency in MSSQL and writing optimized SQL queries and stored procedures. • Hands-on experience with Redis and Celery for task queues and caching. • Expertise in RabbitMQ for messaging systems. • Practic</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>https://www.adzuna.in/details/5819667613?utm_medium=api&amp;utm_source=447522e9</t>
+          <t>https://www.adzuna.in/details/5806699867?utm_medium=api&amp;utm_source=447522e9</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -1885,20 +1885,20 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>2026-09-03 14:42:20</t>
+          <t>2026-09-03 16:28:32</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>8598b9c94bbd4b69cef7</t>
+          <t>72e4255119e60b04397d</t>
         </is>
       </c>
       <c r="K21" t="n">
-        <v>70</v>
+        <v>30</v>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>skill:Python, skill:Java, skill:LLM, skill:RAG, skill:MCP, skill:LangChain, skill:Agentic AI</t>
+          <t>skill:Python, skill:SQL, skill:Git</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
@@ -1916,17 +1916,17 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>af50c92173adc37c2987</t>
+          <t>e064c2f26e0ad99ea307</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Ampera Technologies</t>
+          <t>Freelancer</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Cloud &amp; AI Platform Engineer</t>
+          <t>AI Platform Engineer</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -1936,12 +1936,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Job Description: We are seeking a Cloud &amp; AI Platform Engineer to design and operate AI-native infrastructure that supports large-scale machine learning, generative AI, and agentic AI systems. This role will focus on building secure, scalable, and automated multi-cloud platforms across AWS, Azure, G</t>
+          <t xml:space="preserve">Primary Skills Observability: ELK (Elasticsearch/Kibana), Prometheus, Grafana, PromQL Automation: Java/Vert.x or Python (FastAPI), Shell/Bash, REST/SOAP APIs Cloud &amp; Platform: Docker, Kubernetes, Kafka, Redis Reliability Engineering: Distributed Systems, Microservices, Event-Driven Architecture, DR </t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>https://www.adzuna.in/details/5743193223?utm_medium=api&amp;utm_source=447522e9</t>
+          <t>https://www.adzuna.in/details/5819667613?utm_medium=api&amp;utm_source=447522e9</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -1956,20 +1956,20 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>2026-09-03 14:42:20</t>
+          <t>2026-09-03 16:28:32</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>e93b807a80dea78003e5</t>
+          <t>8598b9c94bbd4b69cef7</t>
         </is>
       </c>
       <c r="K22" t="n">
-        <v>30</v>
+        <v>70</v>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>skill:LLM, skill:AI Agents, skill:Agentic AI</t>
+          <t>skill:Python, skill:Java, skill:LLM, skill:RAG, skill:MCP, skill:LangChain, skill:Agentic AI</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
@@ -1987,17 +1987,17 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>311fb19fb00f4911e61d</t>
+          <t>af50c92173adc37c2987</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Infosys Limited</t>
+          <t>Ampera Technologies</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Agentic AI Engineer</t>
+          <t>Cloud &amp; AI Platform Engineer</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -2007,12 +2007,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Job Description: We are looking for an Agentic AI Engineer to design and build intelligent autonomous AI agents capable of reasoning planning and executing tasks in dynamic environments This role involves working with cutting edge LLMs multi agent frameworks and integrating them into enterprise work</t>
+          <t>Job Description: We are seeking a Cloud &amp; AI Platform Engineer to design and operate AI-native infrastructure that supports large-scale machine learning, generative AI, and agentic AI systems. This role will focus on building secure, scalable, and automated multi-cloud platforms across AWS, Azure, G</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>https://www.adzuna.in/details/5856196683?utm_medium=api&amp;utm_source=447522e9</t>
+          <t>https://www.adzuna.in/details/5743193223?utm_medium=api&amp;utm_source=447522e9</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -2027,20 +2027,20 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>2026-09-03 14:42:20</t>
+          <t>2026-09-03 16:28:32</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>b4d86688855294caa1f5</t>
+          <t>e93b807a80dea78003e5</t>
         </is>
       </c>
       <c r="K23" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>skill:AI Agents, skill:Agentic AI</t>
+          <t>skill:LLM, skill:AI Agents, skill:Agentic AI</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
@@ -2058,7 +2058,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>cf0c42e653989652a580</t>
+          <t>311fb19fb00f4911e61d</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2078,12 +2078,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Job Description: We are seeking a talented and enthusiastic Generative AI Engineer to join our growing AI practice The ideal candidate should have hands on experience in developing Generative AI solutions using Large Language Models LLMs Retrieval Augmented Generation RAG and Python Exposure to clou</t>
+          <t>Job Description: We are looking for an Agentic AI Engineer to design and build intelligent autonomous AI agents capable of reasoning planning and executing tasks in dynamic environments This role involves working with cutting edge LLMs multi agent frameworks and integrating them into enterprise work</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>https://www.adzuna.in/details/5856196541?utm_medium=api&amp;utm_source=447522e9</t>
+          <t>https://www.adzuna.in/details/5856196683?utm_medium=api&amp;utm_source=447522e9</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -2098,20 +2098,20 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>2026-09-03 14:42:20</t>
+          <t>2026-09-03 16:28:32</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>27a48387e067aa38e2bf</t>
+          <t>b4d86688855294caa1f5</t>
         </is>
       </c>
       <c r="K24" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>skill:Python, skill:RAG, skill:Agentic AI</t>
+          <t>skill:AI Agents, skill:Agentic AI</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
@@ -2129,17 +2129,17 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>9ee7c8bccd18fb65df78</t>
+          <t>cf0c42e653989652a580</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Deqode</t>
+          <t>Infosys Limited</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>GenAI &amp; Agentic AI Engineer</t>
+          <t>Agentic AI Engineer</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -2149,12 +2149,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Role Summary We are seeking a skilled GenAI &amp; Agentic AI Engineer with strong experience in building end‑to‑end AI/ML solutions, Generative AI applications, and agent‑based automation workflows. The ideal candidate will have a solid background in machine learning along with hands‑on expertise in LLM</t>
+          <t>Job Description: We are seeking a talented and enthusiastic Generative AI Engineer to join our growing AI practice The ideal candidate should have hands on experience in developing Generative AI solutions using Large Language Models LLMs Retrieval Augmented Generation RAG and Python Exposure to clou</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>https://www.adzuna.in/details/5818254504?utm_medium=api&amp;utm_source=447522e9</t>
+          <t>https://www.adzuna.in/details/5856196541?utm_medium=api&amp;utm_source=447522e9</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -2169,20 +2169,20 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>2026-09-03 14:42:20</t>
+          <t>2026-09-03 16:28:32</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>03332746a9e8bdbcf53b</t>
+          <t>27a48387e067aa38e2bf</t>
         </is>
       </c>
       <c r="K25" t="n">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>skill:RAG, skill:Vector Databases, skill:LangChain, skill:Agentic AI</t>
+          <t>skill:Python, skill:RAG, skill:Agentic AI</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
@@ -2200,17 +2200,17 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>fa3e1a42cbbcfe984440</t>
+          <t>9ee7c8bccd18fb65df78</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Techwise Digital</t>
+          <t>Deqode</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Generative AI &amp; Agentic AI Engineer</t>
+          <t>GenAI &amp; Agentic AI Engineer</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -2220,12 +2220,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>We are seeking a skilled Generative AI Engineer to develop and deploy intelligent, production-ready AI applications using LLMs and agent-based architectures. The candidate will work on building solutions that combine enterprise data, APIs, knowledge repositories, and AI models to solve real-world bu</t>
+          <t>Role Summary We are seeking a skilled GenAI &amp; Agentic AI Engineer with strong experience in building end‑to‑end AI/ML solutions, Generative AI applications, and agent‑based automation workflows. The ideal candidate will have a solid background in machine learning along with hands‑on expertise in LLM</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>https://www.adzuna.in/details/5860488267?utm_medium=api&amp;utm_source=447522e9</t>
+          <t>https://www.adzuna.in/details/5818254504?utm_medium=api&amp;utm_source=447522e9</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -2240,20 +2240,20 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>2026-09-03 14:42:20</t>
+          <t>2026-09-03 16:28:32</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>ea1aa592417dcf430ddd</t>
+          <t>03332746a9e8bdbcf53b</t>
         </is>
       </c>
       <c r="K26" t="n">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>skill:Python, skill:RAG, skill:Agentic AI</t>
+          <t>skill:RAG, skill:Vector Databases, skill:LangChain, skill:Agentic AI</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
@@ -2271,17 +2271,17 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>cf2732cd1a39a42758bf</t>
+          <t>fa3e1a42cbbcfe984440</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Levi Strauss</t>
+          <t>Techwise Digital</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>SAP Retail &amp; Supply Chain - Agentic AI Engineer</t>
+          <t>Generative AI &amp; Agentic AI Engineer</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -2291,12 +2291,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Job Location: Warsaw, Poland Calling all originals: At Levi Strauss &amp; Co., you can be yourself — and be part of something bigger. We’re a company of people who like to forge our own path and leave the world better than we found it. Who believe that what makes us different makes us stronger. So add y</t>
+          <t>We are seeking a skilled Generative AI Engineer to develop and deploy intelligent, production-ready AI applications using LLMs and agent-based architectures. The candidate will work on building solutions that combine enterprise data, APIs, knowledge repositories, and AI models to solve real-world bu</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>https://www.adzuna.in/details/5856965767?utm_medium=api&amp;utm_source=447522e9</t>
+          <t>https://www.adzuna.in/details/5860488267?utm_medium=api&amp;utm_source=447522e9</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -2311,20 +2311,20 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>2026-09-03 14:42:20</t>
+          <t>2026-09-03 16:28:32</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>449076581da53b8b0e2c</t>
+          <t>ea1aa592417dcf430ddd</t>
         </is>
       </c>
       <c r="K27" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>skill:AI Agents, skill:Agentic AI</t>
+          <t>skill:Python, skill:RAG, skill:Agentic AI</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
@@ -2342,32 +2342,32 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>be9947e662597926015b</t>
+          <t>cf2732cd1a39a42758bf</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Trigent Software Private Limited</t>
+          <t>Levi Strauss</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Full Stack Engineer</t>
+          <t>SAP Retail &amp; Supply Chain - Agentic AI Engineer</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Richmond Town, Bangalore</t>
+          <t>Bangalore, Karnataka</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Must-Have Skills Frontend Strong JavaScript fundamentals (ES6, async/await, closures) React experience preferred (hooks, state management, component architecture) Backend Proficient in Python, writing production-grade code Hands-on experience with FastAPI or Flask for building REST APIs Database Exp</t>
+          <t>Job Location: Warsaw, Poland Calling all originals: At Levi Strauss &amp; Co., you can be yourself — and be part of something bigger. We’re a company of people who like to forge our own path and leave the world better than we found it. Who believe that what makes us different makes us stronger. So add y</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>https://www.adzuna.in/details/5867507549?utm_medium=api&amp;utm_source=447522e9</t>
+          <t>https://www.adzuna.in/details/5856965767?utm_medium=api&amp;utm_source=447522e9</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -2382,20 +2382,20 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>2026-09-03 14:42:20</t>
+          <t>2026-09-03 16:28:32</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>f5812926dbe4c720e676</t>
+          <t>449076581da53b8b0e2c</t>
         </is>
       </c>
       <c r="K28" t="n">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>skill:Python, skill:JavaScript, skill:SQL, skill:REST APIs</t>
+          <t>skill:AI Agents, skill:Agentic AI</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
@@ -2413,7 +2413,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>4cabe1a20fc46c23e821</t>
+          <t>be9947e662597926015b</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2438,7 +2438,7 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>https://www.adzuna.in/details/5867507551?utm_medium=api&amp;utm_source=447522e9</t>
+          <t>https://www.adzuna.in/details/5867507549?utm_medium=api&amp;utm_source=447522e9</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -2453,7 +2453,7 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>2026-09-03 14:42:20</t>
+          <t>2026-09-03 16:28:32</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -2480,6 +2480,77 @@
         </is>
       </c>
       <c r="O29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>4cabe1a20fc46c23e821</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Trigent Software Private Limited</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Full Stack Engineer</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Richmond Town, Bangalore</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Must-Have Skills Frontend Strong JavaScript fundamentals (ES6, async/await, closures) React experience preferred (hooks, state management, component architecture) Backend Proficient in Python, writing production-grade code Hands-on experience with FastAPI or Flask for building REST APIs Database Exp</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>https://www.adzuna.in/details/5867507551?utm_medium=api&amp;utm_source=447522e9</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>adzuna</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>2026-09-03 12:39:34</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>2026-09-03 16:28:32</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>f5812926dbe4c720e676</t>
+        </is>
+      </c>
+      <c r="K30" t="n">
+        <v>40</v>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>skill:Python, skill:JavaScript, skill:SQL, skill:REST APIs</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O30" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/akash_jobs.xlsx
+++ b/data/akash_jobs.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O30"/>
+  <dimension ref="A1:O29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -536,7 +536,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>2026-09-03 16:28:32</t>
+          <t>2026-09-04 02:26:43</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -607,7 +607,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>2026-09-03 16:28:32</t>
+          <t>2026-09-04 02:26:43</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -678,7 +678,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>2026-09-03 16:28:32</t>
+          <t>2026-09-04 02:26:43</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -749,7 +749,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>2026-09-03 16:28:32</t>
+          <t>2026-09-04 02:26:43</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -820,7 +820,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>2026-09-03 16:28:32</t>
+          <t>2026-09-04 02:26:43</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -891,7 +891,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>2026-09-03 16:28:32</t>
+          <t>2026-09-04 02:26:43</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -962,7 +962,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>2026-09-03 16:28:32</t>
+          <t>2026-09-04 02:26:43</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1033,7 +1033,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>2026-09-03 16:28:32</t>
+          <t>2026-09-04 02:26:43</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>2026-09-03 16:28:32</t>
+          <t>2026-09-04 02:26:43</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1175,7 +1175,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>2026-09-03 16:28:32</t>
+          <t>2026-09-04 02:26:43</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1246,7 +1246,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>2026-09-03 16:28:32</t>
+          <t>2026-09-04 02:26:43</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1317,7 +1317,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>2026-09-03 16:28:32</t>
+          <t>2026-09-04 02:26:43</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -1388,7 +1388,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>2026-09-03 16:28:32</t>
+          <t>2026-09-04 02:26:43</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -1459,7 +1459,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>2026-09-03 16:28:32</t>
+          <t>2026-09-04 02:26:43</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -1530,7 +1530,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>2026-09-03 16:28:32</t>
+          <t>2026-09-04 02:26:43</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -1601,7 +1601,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>2026-09-03 16:28:32</t>
+          <t>2026-09-04 02:26:43</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -1672,7 +1672,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>2026-09-03 16:28:32</t>
+          <t>2026-09-04 02:26:43</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -1743,7 +1743,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>2026-09-03 16:28:32</t>
+          <t>2026-09-04 02:26:43</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -1774,12 +1774,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>bedebd0e647137fbab9e</t>
+          <t>78723e7ad5a8abc08a88</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Zorba Consulting India</t>
+          <t>Conneqt Business Solutions Limited</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1794,12 +1794,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t xml:space="preserve">Role Overview We are looking for an experienced Python Developer with strong hands-on expertise in Python coding, Streamlit, Flask, and FastAPI . The candidate will be responsible for developing Python-based services, Streamlit applications, automation scripts, API integrations, and data-processing </t>
+          <t>Required Skills and Qualifications: • Strong experience in Python for backend development. • Proficiency in MSSQL and writing optimized SQL queries and stored procedures. • Hands-on experience with Redis and Celery for task queues and caching. • Expertise in RabbitMQ for messaging systems. • Practic</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>https://www.adzuna.in/details/5857693060?utm_medium=api&amp;utm_source=447522e9</t>
+          <t>https://www.adzuna.in/details/5806699867?utm_medium=api&amp;utm_source=447522e9</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -1814,20 +1814,20 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>2026-09-03 16:28:32</t>
+          <t>2026-09-04 02:26:43</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>443a693318c3c6f3b107</t>
+          <t>72e4255119e60b04397d</t>
         </is>
       </c>
       <c r="K20" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>skill:Python, skill:SQL</t>
+          <t>skill:Python, skill:SQL, skill:Git</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
@@ -1845,17 +1845,17 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>78723e7ad5a8abc08a88</t>
+          <t>e064c2f26e0ad99ea307</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Conneqt Business Solutions Limited</t>
+          <t>Freelancer</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Python Developer</t>
+          <t>AI Platform Engineer</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -1865,12 +1865,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Required Skills and Qualifications: • Strong experience in Python for backend development. • Proficiency in MSSQL and writing optimized SQL queries and stored procedures. • Hands-on experience with Redis and Celery for task queues and caching. • Expertise in RabbitMQ for messaging systems. • Practic</t>
+          <t xml:space="preserve">Primary Skills Observability: ELK (Elasticsearch/Kibana), Prometheus, Grafana, PromQL Automation: Java/Vert.x or Python (FastAPI), Shell/Bash, REST/SOAP APIs Cloud &amp; Platform: Docker, Kubernetes, Kafka, Redis Reliability Engineering: Distributed Systems, Microservices, Event-Driven Architecture, DR </t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>https://www.adzuna.in/details/5806699867?utm_medium=api&amp;utm_source=447522e9</t>
+          <t>https://www.adzuna.in/details/5819667613?utm_medium=api&amp;utm_source=447522e9</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -1885,20 +1885,20 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>2026-09-03 16:28:32</t>
+          <t>2026-09-04 02:26:43</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>72e4255119e60b04397d</t>
+          <t>8598b9c94bbd4b69cef7</t>
         </is>
       </c>
       <c r="K21" t="n">
-        <v>30</v>
+        <v>70</v>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>skill:Python, skill:SQL, skill:Git</t>
+          <t>skill:Python, skill:Java, skill:LLM, skill:RAG, skill:MCP, skill:LangChain, skill:Agentic AI</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
@@ -1916,17 +1916,17 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>e064c2f26e0ad99ea307</t>
+          <t>af50c92173adc37c2987</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Freelancer</t>
+          <t>Ampera Technologies</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>AI Platform Engineer</t>
+          <t>Cloud &amp; AI Platform Engineer</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -1936,12 +1936,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t xml:space="preserve">Primary Skills Observability: ELK (Elasticsearch/Kibana), Prometheus, Grafana, PromQL Automation: Java/Vert.x or Python (FastAPI), Shell/Bash, REST/SOAP APIs Cloud &amp; Platform: Docker, Kubernetes, Kafka, Redis Reliability Engineering: Distributed Systems, Microservices, Event-Driven Architecture, DR </t>
+          <t>Job Description: We are seeking a Cloud &amp; AI Platform Engineer to design and operate AI-native infrastructure that supports large-scale machine learning, generative AI, and agentic AI systems. This role will focus on building secure, scalable, and automated multi-cloud platforms across AWS, Azure, G</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>https://www.adzuna.in/details/5819667613?utm_medium=api&amp;utm_source=447522e9</t>
+          <t>https://www.adzuna.in/details/5743193223?utm_medium=api&amp;utm_source=447522e9</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -1956,20 +1956,20 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>2026-09-03 16:28:32</t>
+          <t>2026-09-04 02:26:43</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>8598b9c94bbd4b69cef7</t>
+          <t>e93b807a80dea78003e5</t>
         </is>
       </c>
       <c r="K22" t="n">
-        <v>70</v>
+        <v>30</v>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>skill:Python, skill:Java, skill:LLM, skill:RAG, skill:MCP, skill:LangChain, skill:Agentic AI</t>
+          <t>skill:LLM, skill:AI Agents, skill:Agentic AI</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
@@ -1987,17 +1987,17 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>af50c92173adc37c2987</t>
+          <t>311fb19fb00f4911e61d</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Ampera Technologies</t>
+          <t>Infosys Limited</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Cloud &amp; AI Platform Engineer</t>
+          <t>Agentic AI Engineer</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -2007,12 +2007,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Job Description: We are seeking a Cloud &amp; AI Platform Engineer to design and operate AI-native infrastructure that supports large-scale machine learning, generative AI, and agentic AI systems. This role will focus on building secure, scalable, and automated multi-cloud platforms across AWS, Azure, G</t>
+          <t>Job Description: We are looking for an Agentic AI Engineer to design and build intelligent autonomous AI agents capable of reasoning planning and executing tasks in dynamic environments This role involves working with cutting edge LLMs multi agent frameworks and integrating them into enterprise work</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>https://www.adzuna.in/details/5743193223?utm_medium=api&amp;utm_source=447522e9</t>
+          <t>https://www.adzuna.in/details/5856196683?utm_medium=api&amp;utm_source=447522e9</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -2027,20 +2027,20 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>2026-09-03 16:28:32</t>
+          <t>2026-09-04 02:26:43</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>e93b807a80dea78003e5</t>
+          <t>b4d86688855294caa1f5</t>
         </is>
       </c>
       <c r="K23" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>skill:LLM, skill:AI Agents, skill:Agentic AI</t>
+          <t>skill:AI Agents, skill:Agentic AI</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
@@ -2058,7 +2058,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>311fb19fb00f4911e61d</t>
+          <t>cf0c42e653989652a580</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2078,12 +2078,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Job Description: We are looking for an Agentic AI Engineer to design and build intelligent autonomous AI agents capable of reasoning planning and executing tasks in dynamic environments This role involves working with cutting edge LLMs multi agent frameworks and integrating them into enterprise work</t>
+          <t>Job Description: We are seeking a talented and enthusiastic Generative AI Engineer to join our growing AI practice The ideal candidate should have hands on experience in developing Generative AI solutions using Large Language Models LLMs Retrieval Augmented Generation RAG and Python Exposure to clou</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>https://www.adzuna.in/details/5856196683?utm_medium=api&amp;utm_source=447522e9</t>
+          <t>https://www.adzuna.in/details/5856196541?utm_medium=api&amp;utm_source=447522e9</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -2098,20 +2098,20 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>2026-09-03 16:28:32</t>
+          <t>2026-09-04 02:26:43</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>b4d86688855294caa1f5</t>
+          <t>27a48387e067aa38e2bf</t>
         </is>
       </c>
       <c r="K24" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>skill:AI Agents, skill:Agentic AI</t>
+          <t>skill:Python, skill:RAG, skill:Agentic AI</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
@@ -2129,17 +2129,17 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>cf0c42e653989652a580</t>
+          <t>9ee7c8bccd18fb65df78</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Infosys Limited</t>
+          <t>Deqode</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Agentic AI Engineer</t>
+          <t>GenAI &amp; Agentic AI Engineer</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -2149,12 +2149,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Job Description: We are seeking a talented and enthusiastic Generative AI Engineer to join our growing AI practice The ideal candidate should have hands on experience in developing Generative AI solutions using Large Language Models LLMs Retrieval Augmented Generation RAG and Python Exposure to clou</t>
+          <t>Role Summary We are seeking a skilled GenAI &amp; Agentic AI Engineer with strong experience in building end‑to‑end AI/ML solutions, Generative AI applications, and agent‑based automation workflows. The ideal candidate will have a solid background in machine learning along with hands‑on expertise in LLM</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>https://www.adzuna.in/details/5856196541?utm_medium=api&amp;utm_source=447522e9</t>
+          <t>https://www.adzuna.in/details/5818254504?utm_medium=api&amp;utm_source=447522e9</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -2169,20 +2169,20 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>2026-09-03 16:28:32</t>
+          <t>2026-09-04 02:26:43</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>27a48387e067aa38e2bf</t>
+          <t>03332746a9e8bdbcf53b</t>
         </is>
       </c>
       <c r="K25" t="n">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>skill:Python, skill:RAG, skill:Agentic AI</t>
+          <t>skill:RAG, skill:Vector Databases, skill:LangChain, skill:Agentic AI</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
@@ -2200,17 +2200,17 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>9ee7c8bccd18fb65df78</t>
+          <t>fa3e1a42cbbcfe984440</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Deqode</t>
+          <t>Techwise Digital</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>GenAI &amp; Agentic AI Engineer</t>
+          <t>Generative AI &amp; Agentic AI Engineer</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -2220,12 +2220,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Role Summary We are seeking a skilled GenAI &amp; Agentic AI Engineer with strong experience in building end‑to‑end AI/ML solutions, Generative AI applications, and agent‑based automation workflows. The ideal candidate will have a solid background in machine learning along with hands‑on expertise in LLM</t>
+          <t>We are seeking a skilled Generative AI Engineer to develop and deploy intelligent, production-ready AI applications using LLMs and agent-based architectures. The candidate will work on building solutions that combine enterprise data, APIs, knowledge repositories, and AI models to solve real-world bu</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>https://www.adzuna.in/details/5818254504?utm_medium=api&amp;utm_source=447522e9</t>
+          <t>https://www.adzuna.in/details/5860488267?utm_medium=api&amp;utm_source=447522e9</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -2240,20 +2240,20 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>2026-09-03 16:28:32</t>
+          <t>2026-09-04 02:26:43</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>03332746a9e8bdbcf53b</t>
+          <t>ea1aa592417dcf430ddd</t>
         </is>
       </c>
       <c r="K26" t="n">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>skill:RAG, skill:Vector Databases, skill:LangChain, skill:Agentic AI</t>
+          <t>skill:Python, skill:RAG, skill:Agentic AI</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
@@ -2271,17 +2271,17 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>fa3e1a42cbbcfe984440</t>
+          <t>cf2732cd1a39a42758bf</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Techwise Digital</t>
+          <t>Levi Strauss</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Generative AI &amp; Agentic AI Engineer</t>
+          <t>SAP Retail &amp; Supply Chain - Agentic AI Engineer</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -2291,12 +2291,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>We are seeking a skilled Generative AI Engineer to develop and deploy intelligent, production-ready AI applications using LLMs and agent-based architectures. The candidate will work on building solutions that combine enterprise data, APIs, knowledge repositories, and AI models to solve real-world bu</t>
+          <t>Job Location: Warsaw, Poland Calling all originals: At Levi Strauss &amp; Co., you can be yourself — and be part of something bigger. We’re a company of people who like to forge our own path and leave the world better than we found it. Who believe that what makes us different makes us stronger. So add y</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>https://www.adzuna.in/details/5860488267?utm_medium=api&amp;utm_source=447522e9</t>
+          <t>https://www.adzuna.in/details/5856965767?utm_medium=api&amp;utm_source=447522e9</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -2311,20 +2311,20 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>2026-09-03 16:28:32</t>
+          <t>2026-09-04 02:26:43</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>ea1aa592417dcf430ddd</t>
+          <t>449076581da53b8b0e2c</t>
         </is>
       </c>
       <c r="K27" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>skill:Python, skill:RAG, skill:Agentic AI</t>
+          <t>skill:AI Agents, skill:Agentic AI</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
@@ -2342,32 +2342,32 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>cf2732cd1a39a42758bf</t>
+          <t>be9947e662597926015b</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Levi Strauss</t>
+          <t>Trigent Software Private Limited</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>SAP Retail &amp; Supply Chain - Agentic AI Engineer</t>
+          <t>Full Stack Engineer</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Bangalore, Karnataka</t>
+          <t>Richmond Town, Bangalore</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Job Location: Warsaw, Poland Calling all originals: At Levi Strauss &amp; Co., you can be yourself — and be part of something bigger. We’re a company of people who like to forge our own path and leave the world better than we found it. Who believe that what makes us different makes us stronger. So add y</t>
+          <t>Must-Have Skills Frontend Strong JavaScript fundamentals (ES6, async/await, closures) React experience preferred (hooks, state management, component architecture) Backend Proficient in Python, writing production-grade code Hands-on experience with FastAPI or Flask for building REST APIs Database Exp</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>https://www.adzuna.in/details/5856965767?utm_medium=api&amp;utm_source=447522e9</t>
+          <t>https://www.adzuna.in/details/5867507549?utm_medium=api&amp;utm_source=447522e9</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -2382,20 +2382,20 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>2026-09-03 16:28:32</t>
+          <t>2026-09-04 02:26:43</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>449076581da53b8b0e2c</t>
+          <t>f5812926dbe4c720e676</t>
         </is>
       </c>
       <c r="K28" t="n">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>skill:AI Agents, skill:Agentic AI</t>
+          <t>skill:Python, skill:JavaScript, skill:SQL, skill:REST APIs</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
@@ -2413,7 +2413,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>be9947e662597926015b</t>
+          <t>4cabe1a20fc46c23e821</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2438,7 +2438,7 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>https://www.adzuna.in/details/5867507549?utm_medium=api&amp;utm_source=447522e9</t>
+          <t>https://www.adzuna.in/details/5867507551?utm_medium=api&amp;utm_source=447522e9</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -2453,7 +2453,7 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>2026-09-03 16:28:32</t>
+          <t>2026-09-04 02:26:43</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -2480,77 +2480,6 @@
         </is>
       </c>
       <c r="O29" t="inlineStr"/>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>4cabe1a20fc46c23e821</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>Trigent Software Private Limited</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Full Stack Engineer</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>Richmond Town, Bangalore</t>
-        </is>
-      </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>Must-Have Skills Frontend Strong JavaScript fundamentals (ES6, async/await, closures) React experience preferred (hooks, state management, component architecture) Backend Proficient in Python, writing production-grade code Hands-on experience with FastAPI or Flask for building REST APIs Database Exp</t>
-        </is>
-      </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>https://www.adzuna.in/details/5867507551?utm_medium=api&amp;utm_source=447522e9</t>
-        </is>
-      </c>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t>adzuna</t>
-        </is>
-      </c>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t>2026-09-03 12:39:34</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>2026-09-03 16:28:32</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>f5812926dbe4c720e676</t>
-        </is>
-      </c>
-      <c r="K30" t="n">
-        <v>40</v>
-      </c>
-      <c r="L30" t="inlineStr">
-        <is>
-          <t>skill:Python, skill:JavaScript, skill:SQL, skill:REST APIs</t>
-        </is>
-      </c>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="N30" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="O30" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/akash_jobs.xlsx
+++ b/data/akash_jobs.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O1"/>
+  <dimension ref="A1:O2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -492,6 +492,74 @@
           <t>Notes</t>
         </is>
       </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>b089a3cfab02f278c172</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>capco</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>QA Automation Engineer</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr"/>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>&amp;lt;h3&amp;gt;Shape the Future of Financial Services with Capco&amp;lt;/h3&amp;gt;
+&amp;lt;p&amp;gt;At Capco, we specialize in management consulting and software development, partnering with leading international banks and insurance companies across Western Europe. Our innovative approach and collaborative culture make</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/capco/qa-automation-engineer-118845</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>2026-09-10 15:42:24</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>2026-09-10 15:42:24</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>b170f1c2eea6a07ed122</t>
+        </is>
+      </c>
+      <c r="K2" t="n">
+        <v>40</v>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>skill:Java, skill:SQL, skill:REST APIs, skill:Git</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/akash_jobs.xlsx
+++ b/data/akash_jobs.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O2"/>
+  <dimension ref="A1:O1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -492,74 +492,6 @@
           <t>Notes</t>
         </is>
       </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>b089a3cfab02f278c172</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>capco</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>QA Automation Engineer</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr"/>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>&amp;lt;h3&amp;gt;Shape the Future of Financial Services with Capco&amp;lt;/h3&amp;gt;
-&amp;lt;p&amp;gt;At Capco, we specialize in management consulting and software development, partnering with leading international banks and insurance companies across Western Europe. Our innovative approach and collaborative culture make</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>https://www.arbeitnow.com/jobs/companies/capco/qa-automation-engineer-118845</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>arbeitnow</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>2026-09-10 15:42:24</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>2026-09-10 15:42:24</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>b170f1c2eea6a07ed122</t>
-        </is>
-      </c>
-      <c r="K2" t="n">
-        <v>40</v>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>skill:Java, skill:SQL, skill:REST APIs, skill:Git</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
